--- a/重点商品CA別進捗_2026年4月.xlsx
+++ b/重点商品CA別進捗_2026年4月.xlsx
@@ -16,13 +16,13 @@
     <sheet name="クエスト5・U-Car石川" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'石川'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'亀本'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'神山'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'森'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'北檜山'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'江差'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'クエスト5・U-Car石川'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'石川'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'亀本'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'神山'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'森'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'北檜山'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'江差'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'クエスト5・U-Car石川'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -213,7 +213,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -239,34 +239,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="9">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="10">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="11">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="12">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="13">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="14">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="15">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -292,28 +271,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>2</v>
-              </pt>
-              <pt idx="9">
-                <v>2</v>
-              </pt>
-              <pt idx="10">
-                <v>1</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
-                <v>0</v>
+                <v>5</v>
               </pt>
             </numLit>
           </val>
@@ -359,7 +317,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -377,6 +335,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -427,7 +393,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -453,34 +419,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="9">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="10">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="11">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="12">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="13">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="14">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="15">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -506,28 +451,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
                 <v>1</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -591,6 +515,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -641,7 +573,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -661,22 +593,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -696,15 +619,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
                 <v>0</v>
               </pt>
             </numLit>
@@ -769,6 +683,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -819,7 +741,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -839,22 +761,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -874,15 +787,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
                 <v>0</v>
               </pt>
             </numLit>
@@ -929,7 +833,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -947,6 +851,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -997,7 +909,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1017,22 +929,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1052,16 +955,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>2</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -1125,6 +1019,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1175,7 +1077,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1195,22 +1097,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1230,16 +1123,7 @@
                 <v>1</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>2</v>
-              </pt>
-              <pt idx="8">
-                <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -1303,6 +1187,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1353,7 +1245,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1373,22 +1265,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -1408,16 +1291,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>5</v>
-              </pt>
-              <pt idx="8">
-                <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>1</v>
+                <v>8</v>
               </pt>
             </numLit>
           </val>
@@ -1463,7 +1337,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="6"/>
+          <max val="8"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -1481,6 +1355,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1531,7 +1413,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1551,22 +1433,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1586,16 +1459,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>2</v>
-              </pt>
-              <pt idx="8">
-                <v>2</v>
-              </pt>
-              <pt idx="9">
-                <v>1</v>
+                <v>6</v>
               </pt>
             </numLit>
           </val>
@@ -1659,6 +1523,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1709,7 +1581,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1729,22 +1601,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1764,15 +1627,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
                 <v>0</v>
               </pt>
             </numLit>
@@ -1837,6 +1691,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1887,7 +1749,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1907,22 +1769,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1942,16 +1795,7 @@
                 <v>3</v>
               </pt>
               <pt idx="6">
-                <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>7</v>
-              </pt>
-              <pt idx="8">
-                <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
+                <v>9</v>
               </pt>
             </numLit>
           </val>
@@ -1997,7 +1841,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="7"/>
+          <max val="9"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -2015,6 +1859,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2065,7 +1917,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -2085,22 +1937,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2120,16 +1963,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -2193,6 +2027,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2243,7 +2085,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -2269,34 +2111,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="9">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="10">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="11">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="12">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="13">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="14">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="15">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2322,27 +2143,6 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
                 <v>0</v>
               </pt>
             </numLit>
@@ -2407,6 +2207,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2457,7 +2265,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -2477,22 +2285,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="10"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2512,15 +2311,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
                 <v>0</v>
               </pt>
             </numLit>
@@ -2585,6 +2375,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2635,7 +2433,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -2652,22 +2450,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>4</v>
               </pt>
@@ -2685,15 +2474,6 @@
               </pt>
               <pt idx="5">
                 <v>2</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -2757,6 +2537,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2807,7 +2595,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -2824,22 +2612,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2856,15 +2635,6 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -2929,6 +2699,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2979,7 +2757,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -2996,22 +2774,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -3028,15 +2797,6 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -3083,7 +2843,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -3101,6 +2861,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3151,7 +2919,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3168,22 +2936,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>5</v>
               </pt>
@@ -3200,16 +2959,7 @@
                 <v>2</v>
               </pt>
               <pt idx="5">
-                <v>2</v>
-              </pt>
-              <pt idx="6">
-                <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -3273,6 +3023,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3323,7 +3081,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3340,22 +3098,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>10</v>
               </pt>
@@ -3372,16 +3121,7 @@
                 <v>2</v>
               </pt>
               <pt idx="5">
-                <v>4</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>1</v>
-              </pt>
-              <pt idx="8">
-                <v>1</v>
+                <v>6</v>
               </pt>
             </numLit>
           </val>
@@ -3445,6 +3185,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3495,7 +3243,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3512,22 +3260,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>6</v>
               </pt>
@@ -3544,16 +3283,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>1</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -3617,6 +3347,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3667,7 +3405,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3684,22 +3422,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>3</v>
               </pt>
@@ -3716,15 +3445,6 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -3789,6 +3509,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3839,7 +3567,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3856,22 +3584,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -3889,15 +3608,6 @@
               </pt>
               <pt idx="5">
                 <v>3</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -3961,6 +3671,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4011,7 +3729,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -4028,22 +3746,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -4060,15 +3769,6 @@
                 <v>1</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -4133,6 +3833,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4183,7 +3891,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -4209,34 +3917,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="9">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="10">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="11">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="12">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="13">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="14">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="15">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -4262,28 +3949,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>2</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>1</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
-                <v>0</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -4347,6 +4013,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4397,7 +4071,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -4414,22 +4088,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="6">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="7">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>3</v>
               </pt>
@@ -4446,15 +4111,6 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -4519,6 +4175,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4569,7 +4233,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -4580,19 +4244,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>今泉　健一</v>
-              </pt>
-              <pt idx="5">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>4</v>
               </pt>
@@ -4604,12 +4262,6 @@
               </pt>
               <pt idx="3">
                 <v>1</v>
-              </pt>
-              <pt idx="4">
-                <v>0</v>
-              </pt>
-              <pt idx="5">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -4673,6 +4325,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4723,7 +4383,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -4734,19 +4394,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>今泉　健一</v>
-              </pt>
-              <pt idx="5">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -4757,12 +4411,6 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
-              </pt>
-              <pt idx="4">
-                <v>0</v>
-              </pt>
-              <pt idx="5">
                 <v>0</v>
               </pt>
             </numLit>
@@ -4827,6 +4475,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4877,7 +4533,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -4888,19 +4544,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>今泉　健一</v>
-              </pt>
-              <pt idx="5">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -4911,13 +4561,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
-              </pt>
-              <pt idx="4">
                 <v>1</v>
-              </pt>
-              <pt idx="5">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -4981,6 +4625,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5031,7 +4683,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -5042,19 +4694,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>今泉　健一</v>
-              </pt>
-              <pt idx="5">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>7</v>
               </pt>
@@ -5066,12 +4712,6 @@
               </pt>
               <pt idx="3">
                 <v>1</v>
-              </pt>
-              <pt idx="4">
-                <v>0</v>
-              </pt>
-              <pt idx="5">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -5135,6 +4775,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5185,7 +4833,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -5196,19 +4844,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>今泉　健一</v>
-              </pt>
-              <pt idx="5">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>8</v>
               </pt>
@@ -5219,13 +4861,7 @@
                 <v>2</v>
               </pt>
               <pt idx="3">
-                <v>2</v>
-              </pt>
-              <pt idx="4">
-                <v>0</v>
-              </pt>
-              <pt idx="5">
-                <v>1</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -5289,6 +4925,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5339,7 +4983,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -5350,19 +4994,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>今泉　健一</v>
-              </pt>
-              <pt idx="5">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>7</v>
               </pt>
@@ -5373,13 +5011,7 @@
                 <v>1</v>
               </pt>
               <pt idx="3">
-                <v>2</v>
-              </pt>
-              <pt idx="4">
-                <v>0</v>
-              </pt>
-              <pt idx="5">
-                <v>1</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -5443,6 +5075,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5493,7 +5133,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -5504,19 +5144,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>今泉　健一</v>
-              </pt>
-              <pt idx="5">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -5528,12 +5162,6 @@
               </pt>
               <pt idx="3">
                 <v>1</v>
-              </pt>
-              <pt idx="4">
-                <v>0</v>
-              </pt>
-              <pt idx="5">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -5597,6 +5225,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5647,7 +5283,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -5658,19 +5294,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>今泉　健一</v>
-              </pt>
-              <pt idx="5">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>15</v>
               </pt>
@@ -5681,13 +5311,7 @@
                 <v>11</v>
               </pt>
               <pt idx="3">
-                <v>3</v>
-              </pt>
-              <pt idx="4">
-                <v>0</v>
-              </pt>
-              <pt idx="5">
-                <v>2</v>
+                <v>5</v>
               </pt>
             </numLit>
           </val>
@@ -5751,6 +5375,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5801,7 +5433,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -5812,19 +5444,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>今泉　健一</v>
-              </pt>
-              <pt idx="5">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -5836,12 +5462,6 @@
               </pt>
               <pt idx="3">
                 <v>1</v>
-              </pt>
-              <pt idx="4">
-                <v>0</v>
-              </pt>
-              <pt idx="5">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -5905,6 +5525,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5955,7 +5583,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -5981,34 +5609,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="9">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="10">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="11">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="12">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="13">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="14">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="15">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -6034,28 +5641,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
                 <v>1</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -6119,6 +5705,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6169,7 +5763,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -6180,19 +5774,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>今泉　健一</v>
-              </pt>
-              <pt idx="5">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -6203,12 +5791,6 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
-              </pt>
-              <pt idx="4">
-                <v>0</v>
-              </pt>
-              <pt idx="5">
                 <v>0</v>
               </pt>
             </numLit>
@@ -6273,6 +5855,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6331,7 +5921,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -6391,7 +5981,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6409,6 +5999,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6467,7 +6065,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -6527,7 +6125,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6545,6 +6143,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6603,7 +6209,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -6663,7 +6269,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6681,6 +6287,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6739,7 +6353,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -6817,6 +6431,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6875,7 +6497,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -6953,6 +6575,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7011,7 +6641,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7071,7 +6701,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7089,6 +6719,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7147,7 +6785,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7225,6 +6863,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7283,7 +6929,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7361,6 +7007,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7419,7 +7073,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7479,7 +7133,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7497,6 +7151,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7547,7 +7209,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -7573,34 +7235,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="9">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="10">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="11">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="12">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="13">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="14">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="15">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>4</v>
               </pt>
@@ -7626,28 +7267,7 @@
                 <v>1</v>
               </pt>
               <pt idx="8">
-                <v>4</v>
-              </pt>
-              <pt idx="9">
-                <v>5</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>2</v>
-              </pt>
-              <pt idx="12">
-                <v>1</v>
-              </pt>
-              <pt idx="13">
-                <v>6</v>
-              </pt>
-              <pt idx="14">
-                <v>4</v>
-              </pt>
-              <pt idx="15">
-                <v>1</v>
+                <v>23</v>
               </pt>
             </numLit>
           </val>
@@ -7693,7 +7313,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="7"/>
+          <max val="23"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7711,6 +7331,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7769,7 +7397,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7829,7 +7457,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7847,6 +7475,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7897,22 +7533,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -7959,7 +7601,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7977,6 +7619,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8027,22 +7677,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -8089,7 +7745,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8107,6 +7763,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8157,22 +7821,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -8219,7 +7889,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8237,6 +7907,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8287,23 +7965,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -8349,7 +8033,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8367,6 +8051,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8417,23 +8109,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -8479,7 +8177,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8497,6 +8195,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8547,22 +8253,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -8609,7 +8321,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8627,6 +8339,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8677,22 +8397,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>3</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -8757,6 +8483,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8807,23 +8541,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -8887,6 +8627,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8937,23 +8685,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -8999,7 +8753,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -9017,6 +8771,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9067,7 +8829,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -9093,34 +8855,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="9">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="10">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="11">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="12">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="13">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="14">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="15">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -9146,28 +8887,7 @@
                 <v>1</v>
               </pt>
               <pt idx="8">
-                <v>4</v>
-              </pt>
-              <pt idx="9">
-                <v>6</v>
-              </pt>
-              <pt idx="10">
-                <v>1</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>2</v>
-              </pt>
-              <pt idx="15">
-                <v>1</v>
+                <v>14</v>
               </pt>
             </numLit>
           </val>
@@ -9213,7 +8933,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="8"/>
+          <max val="14"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -9231,6 +8951,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9281,23 +9009,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -9343,7 +9077,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -9361,6 +9095,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9500,6 +9242,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9639,6 +9389,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9778,6 +9536,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9917,6 +9683,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10056,6 +9830,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10195,6 +9977,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10334,6 +10124,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10473,6 +10271,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10612,6 +10418,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10662,7 +10476,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -10688,34 +10502,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="9">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="10">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="11">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="12">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="13">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="14">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="15">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -10741,28 +10534,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
                 <v>1</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -10826,6 +10598,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10965,6 +10745,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -11015,7 +10803,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -11041,34 +10829,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="9">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="10">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="11">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="12">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="13">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="14">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="15">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>3</v>
               </pt>
@@ -11094,28 +10861,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>4</v>
-              </pt>
-              <pt idx="10">
-                <v>1</v>
-              </pt>
-              <pt idx="11">
-                <v>2</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>1</v>
-              </pt>
-              <pt idx="15">
-                <v>0</v>
+                <v>8</v>
               </pt>
             </numLit>
           </val>
@@ -11179,6 +10925,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -11229,7 +10983,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -11255,34 +11009,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="9">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="10">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="11">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="12">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="13">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="14">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="15">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -11308,28 +11041,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>1</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
-                <v>0</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -11393,6 +11105,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -11405,7 +11125,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11427,7 +11147,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11449,7 +11169,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11471,7 +11191,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11493,7 +11213,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11515,7 +11235,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11537,7 +11257,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11559,7 +11279,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11581,7 +11301,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11603,7 +11323,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -11630,7 +11350,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11652,7 +11372,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11674,7 +11394,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11696,7 +11416,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11718,7 +11438,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11740,7 +11460,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11762,7 +11482,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11784,7 +11504,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11806,7 +11526,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11828,7 +11548,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -11855,7 +11575,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11877,7 +11597,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11899,7 +11619,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11921,7 +11641,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11943,7 +11663,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11965,7 +11685,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11987,7 +11707,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12009,7 +11729,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12031,7 +11751,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12053,7 +11773,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12080,7 +11800,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -12102,7 +11822,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -12124,7 +11844,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -12146,7 +11866,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -12168,7 +11888,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -12190,7 +11910,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -12212,7 +11932,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12234,7 +11954,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12256,7 +11976,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12278,7 +11998,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12305,7 +12025,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -12327,7 +12047,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -12349,7 +12069,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -12371,7 +12091,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -12393,7 +12113,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -12415,7 +12135,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -12437,7 +12157,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12459,7 +12179,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12481,7 +12201,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12503,7 +12223,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12530,7 +12250,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -12552,7 +12272,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -12574,7 +12294,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -12596,7 +12316,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -12618,7 +12338,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -12640,7 +12360,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -12662,7 +12382,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12684,7 +12404,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12706,7 +12426,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12728,7 +12448,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12755,7 +12475,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -12777,7 +12497,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -12799,7 +12519,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -12821,7 +12541,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -12843,7 +12563,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -12865,7 +12585,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -12887,7 +12607,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12909,7 +12629,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12931,7 +12651,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12953,7 +12673,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -13260,1241 +12980,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42.48" customWidth="1" min="1" max="1"/>
-    <col width="42.48" customWidth="1" min="2" max="2"/>
-    <col width="42.48" customWidth="1" min="3" max="3"/>
-    <col width="42.48" customWidth="1" min="4" max="4"/>
-    <col width="42.48" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="9" customWidth="1" min="22" max="22"/>
-    <col width="9" customWidth="1" min="23" max="23"/>
-    <col width="9" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">石川店 CA別進捗(重点10商品) </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>商品名</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>加
-藤
-英
-基</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>川
-村
-正
-敏</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>村
-上
-英
-俊</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>阿
-部
-隆
-二</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>野
-呂
-藍
-亮</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>小
-野
-翼</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>橋
-本
-隆
-志</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>岩
-坪
-公
-夫</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>鈴
-木
-聡</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>石
-澤
-直
-道</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>杉
-澤
-修
-平</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>中
-原
-義
-美</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>落
-合
-典
-彦</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>前
-野
-正
-樹</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>秋
-山
-泰
-賢</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>エンジンリフレッシュ</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>エアコン潤滑剤 NC200マキシクール</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>ウィンドウ撥水12カ月</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>エアコン/ヒーター洗浄12カ月</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Ｆ-Premium</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="W8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="X8" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>クーラントエナジー</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="X9" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>抗菌・抗ウィルスコート</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>ボディーコート3カ月</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="S11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>NISMOオイル / Mobil1オイル （台数）</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>ギヤボックス添加剤　SuperADD1201</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:R13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42.48" customWidth="1" min="1" max="1"/>
-    <col width="42.48" customWidth="1" min="2" max="2"/>
-    <col width="42.48" customWidth="1" min="3" max="3"/>
-    <col width="42.48" customWidth="1" min="4" max="4"/>
-    <col width="42.48" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亀本店 CA別進捗(重点10商品) </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>商品名</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>大
-島
-貞
-男</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>杉
-澤
-修
-平</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>平
-館
-健</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>平
-賀
-崇</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>安
-部
-雅
-史</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>田
-中
-智
-久</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>鈴
-木
-聡</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>阿
-部
-隆
-二</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>前
-野
-正
-樹</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>エンジンリフレッシュ</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>エアコン潤滑剤 NC200マキシクール</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>ウィンドウ撥水12カ月</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>エアコン/ヒーター洗浄12カ月</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Ｆ-Premium</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>クーラントエナジー</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>抗菌・抗ウィルスコート</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>ボディーコート3カ月</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>NISMOオイル / Mobil1オイル （台数）</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>ギヤボックス添加剤　SuperADD1201</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -14518,12 +13003,12 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">神山店 CA別進捗(重点10商品) </t>
+          <t xml:space="preserve">石川店 CA別進捗(重点10商品) </t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -14531,102 +13016,98 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>水
-嶋
-規
-雄</t>
+          <t>加
+藤
+英
+基</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>竹
+          <t>川
 村
-優
-希</t>
+正
+敏</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>竹
-内
-杏</t>
+          <t>村
+上
+英
+俊</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>芳
-賀
-芳
-勝</t>
+          <t>阿
+部
+隆
+二</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>中
-原
-義
-美</t>
+          <t>野
+呂
+藍
+亮</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>小
+野
+翼</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>鈴
-木
-聡</t>
+          <t>橋
+本
+隆
+志</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>落
-合
-典
-彦</t>
+          <t>岩
+坪
+公
+夫</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>秋
-山
-泰
-賢</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>0</v>
@@ -14635,10 +13116,10 @@
         <v>0</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -14672,7 +13153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -14682,13 +13163,13 @@
         <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>0</v>
@@ -14703,75 +13184,75 @@
         <v>0</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" s="4" t="n">
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -14781,31 +13262,31 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="4" t="n">
+      <c r="P9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q9" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -14815,13 +13296,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="4" t="n">
         <v>0</v>
@@ -14839,7 +13320,7 @@
         <v>0</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -14849,22 +13330,22 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O11" s="4" t="n">
         <v>0</v>
@@ -14873,7 +13354,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -14889,13 +13370,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -14907,7 +13388,7 @@
         <v>0</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -14917,16 +13398,16 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" s="4" t="n">
         <v>0</v>
@@ -14941,17 +13422,398 @@
         <v>0</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42.48" customWidth="1" min="1" max="1"/>
+    <col width="42.48" customWidth="1" min="2" max="2"/>
+    <col width="42.48" customWidth="1" min="3" max="3"/>
+    <col width="42.48" customWidth="1" min="4" max="4"/>
+    <col width="42.48" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亀本店 CA別進捗(重点10商品) </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="8" customHeight="1"/>
+    <row r="3" ht="358.5826771653543" customHeight="1">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>商品名</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>大
+島
+貞
+男</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>杉
+澤
+修
+平</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>平
+館
+健</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>平
+賀
+崇</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>安
+部
+雅
+史</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>田
+中
+智
+久</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>そ
+の
+他</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42.51968503937007" customHeight="1">
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>エンジンリフレッシュ</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="358.5826771653543" customHeight="1">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>エアコン潤滑剤 NC200マキシクール</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>ウィンドウ撥水12カ月</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>エアコン/ヒーター洗浄12カ月</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Ｆ-Premium</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>クーラントエナジー</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>抗菌・抗ウィルスコート</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>ボディーコート3カ月</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>NISMOオイル / Mobil1オイル （台数）</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>ギヤボックス添加剤　SuperADD1201</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
+  <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14977,12 +13839,352 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">神山店 CA別進捗(重点10商品) </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="8" customHeight="1"/>
+    <row r="3" ht="358.5826771653543" customHeight="1">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>商品名</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>水
+嶋
+規
+雄</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>竹
+村
+優
+希</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>竹
+内
+杏</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>芳
+賀
+芳
+勝</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>中
+原
+義
+美</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>そ
+の
+他</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42.51968503937007" customHeight="1">
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>エンジンリフレッシュ</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="358.5826771653543" customHeight="1">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>エアコン潤滑剤 NC200マキシクール</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>ウィンドウ撥水12カ月</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>エアコン/ヒーター洗浄12カ月</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Ｆ-Premium</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>クーラントエナジー</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>抗菌・抗ウィルスコート</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>ボディーコート3カ月</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>NISMOオイル / Mobil1オイル （台数）</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>ギヤボックス添加剤　SuperADD1201</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
+  <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42.48" customWidth="1" min="1" max="1"/>
+    <col width="42.48" customWidth="1" min="2" max="2"/>
+    <col width="42.48" customWidth="1" min="3" max="3"/>
+    <col width="42.48" customWidth="1" min="4" max="4"/>
+    <col width="42.48" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">森店 CA別進捗(重点10商品) </t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -15015,34 +14217,13 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>今
-泉
-健
-一</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>秋
-山
-泰
-賢</t>
-        </is>
-      </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -15060,14 +14241,8 @@
       <c r="L4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -15085,14 +14260,8 @@
       <c r="L5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -15108,16 +14277,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -15135,14 +14298,8 @@
       <c r="L7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -15158,13 +14315,7 @@
         <v>2</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -15183,13 +14334,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -15210,12 +14355,6 @@
       <c r="L10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="H11" s="4" t="inlineStr">
@@ -15233,13 +14372,7 @@
         <v>11</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -15260,12 +14393,6 @@
       <c r="L12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="H13" s="4" t="inlineStr">
@@ -15285,14 +14412,9 @@
       <c r="L13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -15327,7 +14449,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -15351,18 +14473,13 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -15378,7 +14495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -15394,7 +14511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -15410,7 +14527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -15426,7 +14543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -15523,6 +14640,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -15535,7 +14653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -15546,6 +14664,7 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -15556,7 +14675,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -15578,8 +14697,15 @@
 一</t>
         </is>
       </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>そ
+の
+他</t>
+        </is>
+      </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -15591,8 +14717,11 @@
       <c r="J4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -15604,8 +14733,11 @@
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -15617,8 +14749,11 @@
       <c r="J6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -15630,8 +14765,11 @@
       <c r="J7" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="K7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -15642,6 +14780,9 @@
       </c>
       <c r="J8" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15656,6 +14797,9 @@
       <c r="J9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="H10" s="4" t="inlineStr">
@@ -15669,6 +14813,9 @@
       <c r="J10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="H11" s="4" t="inlineStr">
@@ -15682,6 +14829,9 @@
       <c r="J11" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="H12" s="4" t="inlineStr">
@@ -15695,6 +14845,9 @@
       <c r="J12" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="H13" s="4" t="inlineStr">
@@ -15708,8 +14861,12 @@
       <c r="J13" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -15746,7 +14903,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -15792,7 +14949,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -15814,7 +14971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -15836,7 +14993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -15858,7 +15015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -15880,7 +15037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -16013,6 +15170,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
